--- a/human_verification/cis_5reviewers_215.xlsx
+++ b/human_verification/cis_5reviewers_215.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15039\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15039\Desktop\ICSE_27_DART\human_verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A4F59A-2F43-43A8-A10C-602172D13224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B26962D-0D7B-4312-BFE4-155E45D0B65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41130" yWindow="2470" windowWidth="16200" windowHeight="9310" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -344,9 +344,6 @@
   </si>
   <si>
     <t>ToDo(ahmed): Handle instances of CompositeEntityDerivedMetrics in upcoming PR</t>
-  </si>
-  <si>
-    <t>TODO remove this once the unified dataset is available. Inserting into both events and transactions datasets lets us simulate what is currently happening via kafka when both the events and transactions consumers are running.</t>
   </si>
   <si>
     <t>TODO(wmak): Need to handle `has` queries, basically check that tags.keys has the value?</t>
@@ -1158,6 +1155,10 @@
     <t>adjudication_detail</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>TODO remove this once the unified dataset is available. Inserting into both events and transactions datasets lets us replicate what is currently happening via kafka when both the events and transactions consumers are running.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1591,100 +1592,100 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="AJ1" s="1" t="s">
         <v>4</v>
@@ -1705,16 +1706,16 @@
         <v>9</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AQ1" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -1722,7 +1723,7 @@
         <v>1121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -2114,10 +2115,10 @@
         <v>20</v>
       </c>
       <c r="AR4" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="AS4" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="AS4" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -2519,10 +2520,10 @@
         <v>20</v>
       </c>
       <c r="AR7" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AS7" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="AS7" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -2665,7 +2666,7 @@
         <v>467</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>16</v>
@@ -3462,10 +3463,10 @@
         <v>20</v>
       </c>
       <c r="AR14" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS14" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="AS14" s="3" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -4281,7 +4282,7 @@
         <v>6355</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>15</v>
@@ -4810,10 +4811,10 @@
         <v>20</v>
       </c>
       <c r="AR24" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS24" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -4821,7 +4822,7 @@
         <v>5357</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>16</v>
@@ -5888,10 +5889,10 @@
         <v>20</v>
       </c>
       <c r="AR32" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS32" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -6293,10 +6294,10 @@
         <v>20</v>
       </c>
       <c r="AR35" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS35" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -7643,10 +7644,10 @@
         <v>20</v>
       </c>
       <c r="AR45" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AS45" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="AS45" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -8586,10 +8587,10 @@
         <v>20</v>
       </c>
       <c r="AR52" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS52" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="AS52" s="3" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -8856,10 +8857,10 @@
         <v>20</v>
       </c>
       <c r="AR54" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS54" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -9135,7 +9136,7 @@
         <v>5233</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>15</v>
@@ -9259,10 +9260,10 @@
         <v>20</v>
       </c>
       <c r="AR57" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AS57" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -9394,10 +9395,10 @@
         <v>20</v>
       </c>
       <c r="AR58" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS58" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:45" ht="40.5" x14ac:dyDescent="0.3">
@@ -10751,7 +10752,7 @@
         <v>7095</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>15</v>
@@ -10886,7 +10887,7 @@
         <v>7159</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>101</v>
+        <v>345</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>15</v>
@@ -11010,10 +11011,10 @@
         <v>20</v>
       </c>
       <c r="AR70" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AS70" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -11021,7 +11022,7 @@
         <v>7453</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>15</v>
@@ -11156,7 +11157,7 @@
         <v>7512</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>16</v>
@@ -11291,7 +11292,7 @@
         <v>7566</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2">
@@ -11424,7 +11425,7 @@
         <v>7619</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>15</v>
@@ -11559,7 +11560,7 @@
         <v>7752</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>15</v>
@@ -11694,7 +11695,7 @@
         <v>7770</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>15</v>
@@ -11829,7 +11830,7 @@
         <v>7783</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>25</v>
@@ -11946,7 +11947,7 @@
         <v>11</v>
       </c>
       <c r="AO77" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP77" s="2"/>
       <c r="AQ77" s="2" t="s">
@@ -11964,7 +11965,7 @@
         <v>8231</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>15</v>
@@ -12099,7 +12100,7 @@
         <v>8334</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>16</v>
@@ -12234,7 +12235,7 @@
         <v>8425</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>15</v>
@@ -12369,7 +12370,7 @@
         <v>8436</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>15</v>
@@ -12504,7 +12505,7 @@
         <v>8682</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2">
@@ -12637,7 +12638,7 @@
         <v>8819</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>15</v>
@@ -12772,7 +12773,7 @@
         <v>8850</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>10</v>
@@ -12907,7 +12908,7 @@
         <v>9022</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>16</v>
@@ -13042,7 +13043,7 @@
         <v>9549</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>15</v>
@@ -13177,7 +13178,7 @@
         <v>9588</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>16</v>
@@ -13312,7 +13313,7 @@
         <v>10069</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>16</v>
@@ -13447,7 +13448,7 @@
         <v>10368</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2">
@@ -13569,10 +13570,10 @@
         <v>20</v>
       </c>
       <c r="AR89" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS89" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -13580,7 +13581,7 @@
         <v>10436</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>25</v>
@@ -13697,7 +13698,7 @@
         <v>11</v>
       </c>
       <c r="AO90" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP90" s="2"/>
       <c r="AQ90" s="2" t="s">
@@ -13715,7 +13716,7 @@
         <v>10744</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2">
@@ -13837,10 +13838,10 @@
         <v>20</v>
       </c>
       <c r="AR91" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS91" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="92" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -13848,7 +13849,7 @@
         <v>10791</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2">
@@ -13970,10 +13971,10 @@
         <v>20</v>
       </c>
       <c r="AR92" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS92" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -13981,7 +13982,7 @@
         <v>10938</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>15</v>
@@ -14116,7 +14117,7 @@
         <v>1099</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>16</v>
@@ -14251,7 +14252,7 @@
         <v>1240</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>16</v>
@@ -14386,7 +14387,7 @@
         <v>1436</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>16</v>
@@ -14521,7 +14522,7 @@
         <v>1727</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>15</v>
@@ -14656,7 +14657,7 @@
         <v>1860</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>25</v>
@@ -14773,7 +14774,7 @@
         <v>11</v>
       </c>
       <c r="AO98" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP98" s="2"/>
       <c r="AQ98" s="2" t="s">
@@ -14791,7 +14792,7 @@
         <v>1952</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>10</v>
@@ -14926,7 +14927,7 @@
         <v>1967</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>10</v>
@@ -15061,7 +15062,7 @@
         <v>2024</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>15</v>
@@ -15196,7 +15197,7 @@
         <v>2152</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2">
@@ -15318,10 +15319,10 @@
         <v>20</v>
       </c>
       <c r="AR102" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS102" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -15329,7 +15330,7 @@
         <v>2325</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2">
@@ -15451,10 +15452,10 @@
         <v>20</v>
       </c>
       <c r="AR103" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS103" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="104" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -15462,7 +15463,7 @@
         <v>2596</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2">
@@ -15584,10 +15585,10 @@
         <v>20</v>
       </c>
       <c r="AR104" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="AS104" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="AS104" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="105" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -15595,7 +15596,7 @@
         <v>2847</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2">
@@ -15717,10 +15718,10 @@
         <v>20</v>
       </c>
       <c r="AR105" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS105" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -15728,7 +15729,7 @@
         <v>3271</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2">
@@ -15850,10 +15851,10 @@
         <v>20</v>
       </c>
       <c r="AR106" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="AS106" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="AS106" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="107" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -15861,7 +15862,7 @@
         <v>3494</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>15</v>
@@ -15996,7 +15997,7 @@
         <v>3640</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>15</v>
@@ -16131,7 +16132,7 @@
         <v>3670</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>10</v>
@@ -16255,10 +16256,10 @@
         <v>20</v>
       </c>
       <c r="AR109" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AS109" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -16266,7 +16267,7 @@
         <v>3902</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2">
@@ -16388,10 +16389,10 @@
         <v>20</v>
       </c>
       <c r="AR110" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS110" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -16399,7 +16400,7 @@
         <v>3913</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2">
@@ -16514,7 +16515,7 @@
         <v>20</v>
       </c>
       <c r="AO111" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AP111" s="2"/>
       <c r="AQ111" s="2" t="s">
@@ -16532,7 +16533,7 @@
         <v>3960</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>15</v>
@@ -16667,7 +16668,7 @@
         <v>3967</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2">
@@ -16782,7 +16783,7 @@
         <v>20</v>
       </c>
       <c r="AO113" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP113" s="2"/>
       <c r="AQ113" s="2" t="s">
@@ -16800,7 +16801,7 @@
         <v>3969</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2">
@@ -16933,7 +16934,7 @@
         <v>4148</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>15</v>
@@ -17068,7 +17069,7 @@
         <v>4166</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2">
@@ -17201,7 +17202,7 @@
         <v>4177</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>10</v>
@@ -17325,10 +17326,10 @@
         <v>20</v>
       </c>
       <c r="AR117" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS117" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -17336,7 +17337,7 @@
         <v>4194</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>15</v>
@@ -17471,7 +17472,7 @@
         <v>4252</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2">
@@ -17604,7 +17605,7 @@
         <v>4296</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>16</v>
@@ -17739,7 +17740,7 @@
         <v>4366</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2">
@@ -17872,7 +17873,7 @@
         <v>4398</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2">
@@ -17987,7 +17988,7 @@
         <v>20</v>
       </c>
       <c r="AO122" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AP122" s="2"/>
       <c r="AQ122" s="2" t="s">
@@ -18005,7 +18006,7 @@
         <v>4466</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>16</v>
@@ -18140,7 +18141,7 @@
         <v>4552</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>15</v>
@@ -18275,7 +18276,7 @@
         <v>4699</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>15</v>
@@ -18410,7 +18411,7 @@
         <v>4811</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>10</v>
@@ -18545,7 +18546,7 @@
         <v>4877</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2">
@@ -18660,7 +18661,7 @@
         <v>20</v>
       </c>
       <c r="AO127" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AP127" s="2"/>
       <c r="AQ127" s="2" t="s">
@@ -18678,7 +18679,7 @@
         <v>5084</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>16</v>
@@ -18813,7 +18814,7 @@
         <v>5185</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>16</v>
@@ -18948,7 +18949,7 @@
         <v>5257</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>16</v>
@@ -19083,7 +19084,7 @@
         <v>5298</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>10</v>
@@ -19218,7 +19219,7 @@
         <v>5444</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2">
@@ -19351,7 +19352,7 @@
         <v>5548</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
@@ -19468,7 +19469,7 @@
         <v>11</v>
       </c>
       <c r="AO133" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AP133" s="2"/>
       <c r="AQ133" s="2" t="s">
@@ -19486,7 +19487,7 @@
         <v>5623</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2">
@@ -19601,7 +19602,7 @@
         <v>20</v>
       </c>
       <c r="AO134" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AP134" s="2"/>
       <c r="AQ134" s="2" t="s">
@@ -19619,7 +19620,7 @@
         <v>1089</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>15</v>
@@ -19754,7 +19755,7 @@
         <v>1292</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2">
@@ -19876,10 +19877,10 @@
         <v>20</v>
       </c>
       <c r="AR136" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS136" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -19887,7 +19888,7 @@
         <v>1317</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>15</v>
@@ -20022,7 +20023,7 @@
         <v>1830</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>10</v>
@@ -20157,7 +20158,7 @@
         <v>2021</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>10</v>
@@ -20281,10 +20282,10 @@
         <v>20</v>
       </c>
       <c r="AR139" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AS139" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -20292,7 +20293,7 @@
         <v>2244</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>16</v>
@@ -20427,7 +20428,7 @@
         <v>2605</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>10</v>
@@ -20562,7 +20563,7 @@
         <v>2655</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>16</v>
@@ -20697,7 +20698,7 @@
         <v>2850</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>10</v>
@@ -20832,7 +20833,7 @@
         <v>3079</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>25</v>
@@ -20956,10 +20957,10 @@
         <v>20</v>
       </c>
       <c r="AR144" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AS144" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -20967,7 +20968,7 @@
         <v>3915</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2">
@@ -21100,7 +21101,7 @@
         <v>3931</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2">
@@ -21233,7 +21234,7 @@
         <v>4162</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2">
@@ -21348,7 +21349,7 @@
         <v>20</v>
       </c>
       <c r="AO147" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP147" s="2"/>
       <c r="AQ147" s="2" t="s">
@@ -21366,7 +21367,7 @@
         <v>4236</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>15</v>
@@ -21501,7 +21502,7 @@
         <v>4668</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2">
@@ -21634,7 +21635,7 @@
         <v>4795</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>16</v>
@@ -21769,7 +21770,7 @@
         <v>4878</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>16</v>
@@ -21904,7 +21905,7 @@
         <v>5272</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>25</v>
@@ -22039,7 +22040,7 @@
         <v>5334</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>15</v>
@@ -22174,7 +22175,7 @@
         <v>5398</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2">
@@ -22307,7 +22308,7 @@
         <v>4665</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>15</v>
@@ -22442,7 +22443,7 @@
         <v>2678</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2">
@@ -22564,10 +22565,10 @@
         <v>20</v>
       </c>
       <c r="AR156" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS156" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="157" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -22575,7 +22576,7 @@
         <v>1452</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>25</v>
@@ -22692,7 +22693,7 @@
         <v>11</v>
       </c>
       <c r="AO157" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP157" s="2"/>
       <c r="AQ157" s="2" t="s">
@@ -22710,7 +22711,7 @@
         <v>5526</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>15</v>
@@ -22845,7 +22846,7 @@
         <v>982</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>15</v>
@@ -22969,10 +22970,10 @@
         <v>20</v>
       </c>
       <c r="AR159" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS159" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="AS159" s="3" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -22980,7 +22981,7 @@
         <v>1211</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2">
@@ -23102,10 +23103,10 @@
         <v>20</v>
       </c>
       <c r="AR160" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS160" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="161" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -23113,7 +23114,7 @@
         <v>1257</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>15</v>
@@ -23248,7 +23249,7 @@
         <v>1353</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>10</v>
@@ -23383,7 +23384,7 @@
         <v>1602</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>15</v>
@@ -23518,7 +23519,7 @@
         <v>1875</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>15</v>
@@ -23635,17 +23636,17 @@
         <v>11</v>
       </c>
       <c r="AO164" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AP164" s="2"/>
       <c r="AQ164" s="3" t="s">
         <v>20</v>
       </c>
       <c r="AR164" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AS164" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -23653,7 +23654,7 @@
         <v>2909</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>16</v>
@@ -23788,7 +23789,7 @@
         <v>2984</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>16</v>
@@ -23923,7 +23924,7 @@
         <v>3446</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>15</v>
@@ -24058,7 +24059,7 @@
         <v>3603</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>16</v>
@@ -24193,7 +24194,7 @@
         <v>4061</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>15</v>
@@ -24310,17 +24311,17 @@
         <v>11</v>
       </c>
       <c r="AO169" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AP169" s="2"/>
       <c r="AQ169" s="3" t="s">
         <v>20</v>
       </c>
       <c r="AR169" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AS169" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -24328,7 +24329,7 @@
         <v>4448</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>16</v>
@@ -24463,7 +24464,7 @@
         <v>4566</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>16</v>
@@ -24598,7 +24599,7 @@
         <v>4614</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2">
@@ -24731,7 +24732,7 @@
         <v>4622</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2">
@@ -24864,7 +24865,7 @@
         <v>4772</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>15</v>
@@ -24999,7 +25000,7 @@
         <v>4822</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>16</v>
@@ -25134,7 +25135,7 @@
         <v>5036</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>16</v>
@@ -25269,7 +25270,7 @@
         <v>5117</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>15</v>
@@ -25404,7 +25405,7 @@
         <v>5374</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>15</v>
@@ -25521,7 +25522,7 @@
         <v>11</v>
       </c>
       <c r="AO178" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AP178" s="2"/>
       <c r="AQ178" s="2" t="s">
@@ -25539,7 +25540,7 @@
         <v>5541</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>16</v>
@@ -25674,7 +25675,7 @@
         <v>5606</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2">
@@ -25807,7 +25808,7 @@
         <v>6373</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>25</v>
@@ -25924,7 +25925,7 @@
         <v>11</v>
       </c>
       <c r="AO181" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP181" s="2"/>
       <c r="AQ181" s="2" t="s">
@@ -25942,7 +25943,7 @@
         <v>6526</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>16</v>
@@ -26077,7 +26078,7 @@
         <v>6750</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>16</v>
@@ -26212,7 +26213,7 @@
         <v>6973</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>25</v>
@@ -26329,7 +26330,7 @@
         <v>20</v>
       </c>
       <c r="AO184" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AP184" s="2"/>
       <c r="AQ184" s="2" t="s">
@@ -26347,7 +26348,7 @@
         <v>6981</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>10</v>
@@ -26482,7 +26483,7 @@
         <v>7115</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>25</v>
@@ -26617,7 +26618,7 @@
         <v>7832</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>16</v>
@@ -26752,7 +26753,7 @@
         <v>8946</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>15</v>
@@ -26887,7 +26888,7 @@
         <v>9994</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>10</v>
@@ -27004,17 +27005,17 @@
         <v>11</v>
       </c>
       <c r="AO189" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AP189" s="2"/>
       <c r="AQ189" s="3" t="s">
         <v>20</v>
       </c>
       <c r="AR189" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AS189" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -27022,7 +27023,7 @@
         <v>6699</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2">
@@ -27137,7 +27138,7 @@
         <v>20</v>
       </c>
       <c r="AO190" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP190" s="2"/>
       <c r="AQ190" s="2" t="s">
@@ -27155,7 +27156,7 @@
         <v>6794</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2">
@@ -27270,7 +27271,7 @@
         <v>20</v>
       </c>
       <c r="AO191" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP191" s="2"/>
       <c r="AQ191" s="2" t="s">
@@ -27288,7 +27289,7 @@
         <v>7158</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2">
@@ -27403,7 +27404,7 @@
         <v>20</v>
       </c>
       <c r="AO192" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP192" s="2"/>
       <c r="AQ192" s="2" t="s">
@@ -27421,7 +27422,7 @@
         <v>7779</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>10</v>
@@ -27556,7 +27557,7 @@
         <v>8426</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>15</v>
@@ -27691,7 +27692,7 @@
         <v>9122</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2">
@@ -27806,7 +27807,7 @@
         <v>20</v>
       </c>
       <c r="AO195" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AP195" s="2"/>
       <c r="AQ195" s="2" t="s">
@@ -27824,7 +27825,7 @@
         <v>9341</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>15</v>
@@ -27959,7 +27960,7 @@
         <v>9418</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>15</v>
@@ -28094,7 +28095,7 @@
         <v>9495</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>15</v>
@@ -28229,7 +28230,7 @@
         <v>9583</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>10</v>
@@ -28364,7 +28365,7 @@
         <v>9762</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2">
@@ -28497,7 +28498,7 @@
         <v>10411</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>16</v>
@@ -28632,7 +28633,7 @@
         <v>10499</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2">
@@ -28754,10 +28755,10 @@
         <v>20</v>
       </c>
       <c r="AR202" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AS202" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="AS202" s="3" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="203" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -28765,7 +28766,7 @@
         <v>10533</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>10</v>
@@ -28889,10 +28890,10 @@
         <v>20</v>
       </c>
       <c r="AR203" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="AS203" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="AS203" s="3" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -28900,7 +28901,7 @@
         <v>10948</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2">
@@ -29022,10 +29023,10 @@
         <v>20</v>
       </c>
       <c r="AR204" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="AS204" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="AS204" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="205" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -29033,7 +29034,7 @@
         <v>6382</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2">
@@ -29166,7 +29167,7 @@
         <v>7005</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>16</v>
@@ -29301,7 +29302,7 @@
         <v>7646</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2">
@@ -29416,7 +29417,7 @@
         <v>20</v>
       </c>
       <c r="AO207" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AP207" s="2"/>
       <c r="AQ207" s="2" t="s">
@@ -29434,7 +29435,7 @@
         <v>8291</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2">
@@ -29549,7 +29550,7 @@
         <v>20</v>
       </c>
       <c r="AO208" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP208" s="2"/>
       <c r="AQ208" s="2" t="s">
@@ -29567,7 +29568,7 @@
         <v>8687</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>25</v>
@@ -29702,7 +29703,7 @@
         <v>9274</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>15</v>
@@ -29837,7 +29838,7 @@
         <v>9648</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>16</v>
@@ -29972,7 +29973,7 @@
         <v>6562</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>15</v>
@@ -30107,7 +30108,7 @@
         <v>7087</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>16</v>
@@ -30242,7 +30243,7 @@
         <v>7112</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2">
@@ -30375,7 +30376,7 @@
         <v>8412</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>16</v>
@@ -30499,10 +30500,10 @@
         <v>20</v>
       </c>
       <c r="AR215" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="AS215" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="AS215" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="216" spans="1:45" ht="27" x14ac:dyDescent="0.3">
@@ -30510,7 +30511,7 @@
         <v>9701</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>10</v>
@@ -30659,15 +30660,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" t="s">
         <v>321</v>
-      </c>
-      <c r="B1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B2">
         <v>215</v>
@@ -30675,7 +30676,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -30683,39 +30684,39 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" t="s">
         <v>325</v>
-      </c>
-      <c r="B4" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B5" t="s">
         <v>327</v>
-      </c>
-      <c r="B5" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B6" t="s">
         <v>329</v>
-      </c>
-      <c r="B6" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B7" t="s">
         <v>331</v>
-      </c>
-      <c r="B7" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B8">
         <v>50</v>
@@ -30723,15 +30724,15 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B9" t="s">
         <v>334</v>
-      </c>
-      <c r="B9" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B10">
         <v>14</v>
@@ -30755,7 +30756,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B13">
         <v>34</v>
@@ -30763,7 +30764,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B14">
         <v>167</v>
@@ -30774,7 +30775,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B15">
         <v>0.69099999999999995</v>
@@ -30782,7 +30783,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B16">
         <v>0.99299999999999999</v>
@@ -30790,7 +30791,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B17" s="5">
         <v>0.874</v>
@@ -30798,7 +30799,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B18">
         <v>0.90800000000000003</v>
@@ -30828,94 +30829,94 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>7</v>
@@ -30927,10 +30928,10 @@
         <v>9</v>
       </c>
       <c r="AJ1" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="27" x14ac:dyDescent="0.3">
@@ -33168,7 +33169,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ21" s="2" t="s">
         <v>11</v>
@@ -33279,7 +33280,7 @@
         <v>3.2</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ22" s="2" t="s">
         <v>11</v>
@@ -33834,7 +33835,7 @@
         <v>7.4</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AJ27" s="2" t="s">
         <v>11</v>
@@ -34058,7 +34059,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ29" s="2" t="s">
         <v>11</v>
@@ -34393,7 +34394,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ32" s="2" t="s">
         <v>11</v>
@@ -34726,7 +34727,7 @@
         <v>3.4</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ35" s="2" t="s">
         <v>11</v>
@@ -35507,7 +35508,7 @@
         <v>5</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AJ42" s="2" t="s">
         <v>11</v>
@@ -35618,7 +35619,7 @@
         <v>3.4</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ43" s="2" t="s">
         <v>11</v>
@@ -35729,7 +35730,7 @@
         <v>6.2</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AJ44" s="2" t="s">
         <v>11</v>
@@ -35840,7 +35841,7 @@
         <v>3.2</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ45" s="2" t="s">
         <v>11</v>
@@ -35951,7 +35952,7 @@
         <v>7.4</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AJ46" s="2" t="s">
         <v>11</v>
@@ -36284,7 +36285,7 @@
         <v>7.2</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AJ49" s="2" t="s">
         <v>11</v>
@@ -36395,7 +36396,7 @@
         <v>2.4</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AJ50" s="2" t="s">
         <v>11</v>
@@ -36536,49 +36537,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36586,7 +36587,7 @@
         <v>1755</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -36628,7 +36629,7 @@
         <v>16</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36636,7 +36637,7 @@
         <v>1875</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>15</v>
@@ -36678,7 +36679,7 @@
         <v>15</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36686,7 +36687,7 @@
         <v>2021</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -36728,7 +36729,7 @@
         <v>10</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36736,7 +36737,7 @@
         <v>3079</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>25</v>
@@ -36778,7 +36779,7 @@
         <v>25</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36786,7 +36787,7 @@
         <v>3670</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -36828,7 +36829,7 @@
         <v>10</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36836,7 +36837,7 @@
         <v>4061</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
@@ -36878,7 +36879,7 @@
         <v>15</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36886,7 +36887,7 @@
         <v>4126</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>15</v>
@@ -36928,7 +36929,7 @@
         <v>15</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36936,7 +36937,7 @@
         <v>4177</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -36978,7 +36979,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -36986,7 +36987,7 @@
         <v>4467</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
@@ -37028,7 +37029,7 @@
         <v>15</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37036,7 +37037,7 @@
         <v>4934</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>25</v>
@@ -37078,7 +37079,7 @@
         <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37086,7 +37087,7 @@
         <v>5233</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>15</v>
@@ -37128,7 +37129,7 @@
         <v>15</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37136,7 +37137,7 @@
         <v>5285</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -37178,7 +37179,7 @@
         <v>10</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37186,7 +37187,7 @@
         <v>5413</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>16</v>
@@ -37228,7 +37229,7 @@
         <v>16</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37236,7 +37237,7 @@
         <v>6150</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>15</v>
@@ -37278,7 +37279,7 @@
         <v>15</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37286,7 +37287,7 @@
         <v>7159</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>15</v>
@@ -37328,7 +37329,7 @@
         <v>15</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37336,7 +37337,7 @@
         <v>8412</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>16</v>
@@ -37378,7 +37379,7 @@
         <v>16</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37386,7 +37387,7 @@
         <v>982</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>15</v>
@@ -37428,7 +37429,7 @@
         <v>15</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37436,7 +37437,7 @@
         <v>9994</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -37478,7 +37479,7 @@
         <v>10</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37486,7 +37487,7 @@
         <v>10368</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>16</v>
@@ -37528,7 +37529,7 @@
         <v>16</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37536,7 +37537,7 @@
         <v>10499</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>16</v>
@@ -37578,7 +37579,7 @@
         <v>16</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37586,7 +37587,7 @@
         <v>10533</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>15</v>
@@ -37628,7 +37629,7 @@
         <v>15</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37636,7 +37637,7 @@
         <v>10744</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>15</v>
@@ -37678,7 +37679,7 @@
         <v>15</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37686,7 +37687,7 @@
         <v>10791</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
@@ -37728,7 +37729,7 @@
         <v>25</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37736,7 +37737,7 @@
         <v>10948</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>16</v>
@@ -37778,7 +37779,7 @@
         <v>16</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37786,7 +37787,7 @@
         <v>1211</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>15</v>
@@ -37828,7 +37829,7 @@
         <v>15</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37836,7 +37837,7 @@
         <v>1292</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>15</v>
@@ -37878,7 +37879,7 @@
         <v>15</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37886,7 +37887,7 @@
         <v>1898</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>16</v>
@@ -37928,7 +37929,7 @@
         <v>16</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37936,7 +37937,7 @@
         <v>2152</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>16</v>
@@ -37978,7 +37979,7 @@
         <v>16</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -37986,7 +37987,7 @@
         <v>2325</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>15</v>
@@ -38028,7 +38029,7 @@
         <v>15</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38036,7 +38037,7 @@
         <v>2596</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>16</v>
@@ -38078,7 +38079,7 @@
         <v>16</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38086,7 +38087,7 @@
         <v>2678</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>15</v>
@@ -38128,7 +38129,7 @@
         <v>15</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38136,7 +38137,7 @@
         <v>2847</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>15</v>
@@ -38178,7 +38179,7 @@
         <v>15</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38186,7 +38187,7 @@
         <v>3271</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>16</v>
@@ -38228,7 +38229,7 @@
         <v>16</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38236,7 +38237,7 @@
         <v>3348</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>15</v>
@@ -38278,7 +38279,7 @@
         <v>15</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38286,7 +38287,7 @@
         <v>3878</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>15</v>
@@ -38328,7 +38329,7 @@
         <v>15</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="27" x14ac:dyDescent="0.3">
@@ -38336,7 +38337,7 @@
         <v>3902</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>10</v>
@@ -38378,7 +38379,7 @@
         <v>10</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
